--- a/02_加值成品/八下/八下2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下2-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下2-3 氧化還原與生活　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下2-3 氧化還原與生活　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>金屬反應難易由什麼決定？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>活性大小</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>鉀/鈉</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>順序</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>活性大金屬能置換活性？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>活性順序</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>反應或氧化</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>小的金屬</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>置換</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>金活性大還小？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>小</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>置換出銅</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>穩定</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>電池把化學能轉成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>小的金屬</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>氧化還原</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>電能</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>鍍鋅是用鋅保護？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>小的金屬</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>鐵</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>活性大小</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>犧牲</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>鐵放入硫酸銅溶液會析出？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>鐵</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>活性大小</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>置換</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>金飾不易變色因為活性？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>小</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>小的金屬</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>鉀/鈉</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>活性大小</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>穩定</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>鎂比鐵活性？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>表面析出銅</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>鉀/鈉</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>較活潑</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>金屬活性大小的排列稱？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>小的金屬</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>活性順序</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>順序</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>活性大的金屬較容易？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>反應或氧化</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>氧化還原</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>鉀/鈉</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>置換出銅</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>活潑</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下2-3 氧化還原與生活　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下2-3 氧化還原與生活　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>鋅片放硫酸銅溶液會？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>置換出銅</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>鉀/鈉</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>活性大小</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>鋅活性大</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>銅放硫酸鋅溶液會反應嗎？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>氧化還原</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>不會</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>銅活性小</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>乾電池屬於哪類反應？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>活性大小</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>氧化還原</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>鐵</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>產電</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>鍍鋅鐵皮刮傷後誰先氧化？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>置換出銅</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>鋅</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>犧牲陽極</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>活性順序中最前面常見金屬？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>表面析出銅</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>鉀/鈉</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>極活潑</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>鐵釘泡硫酸銅變色因為？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>表面析出銅</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>活性大小</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>鐵</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>置換</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>活性小的金屬在自然界常以何存在？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>活性大者置換溶液中活性小者</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>犧牲陽極防船體生鏽</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>鋅活性大先氧化保護鐵</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>元素態(如金)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>穩定</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>犧牲陽極用比被保護金屬活性？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>置換出銅</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>活性大小</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>先氧化</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>鐵放入硫酸銅溶液表面析出？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>氧化還原</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>置換</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>乾電池把化學能轉成什麼能？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>氧化還原</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>電能</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>活性大小</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>轉換</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下2-3 氧化還原與生活　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下2-3 氧化還原與生活　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何鋅能保護鐵而錫不能長久？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>氧化還原持續轉移電子</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>鋅活性&gt;鐵先氧化;錫活性&lt;鐵破損後鐵先鏽</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>氫氣(鎂較活潑)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>活性極小不易氧化</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>活性</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>電池為何能持續產電？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>鋅活性&gt;鐵先氧化;錫活性&lt;鐵破損後鐵先鏽</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>犧牲陽極防船體生鏽</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>氧化還原持續轉移電子</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>氫氣(鎂較活潑)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>機制</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>把鐵鋅銅片與活性排序判斷置換？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>鋅活性&gt;鐵先氧化;錫活性&lt;鐵破損後鐵先鏽</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>活性極小不易氧化</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>氧化還原持續轉移電子</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>活性大者置換溶液中活性小者</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>海邊船體裝鋅塊作用？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>犧牲陽極防船體生鏽</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>活性大於氫者能與酸產氫</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>金,活性小較穩定</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>活性極小不易氧化</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>保護</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>金與銀為何常保光澤？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>鋅活性大先氧化保護鐵</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>金,活性小較穩定</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>氫氣(鎂較活潑)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>活性極小不易氧化</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>穩定</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>鎂條放入稀鹽酸產生氣泡是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>金,活性小較穩定</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>元素態(如金)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>氫氣(鎂較活潑)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>活性大於氫者能與酸產氫</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>反應</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>活性順序如何預測金屬與酸反應？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>活性大於氫者能與酸產氫</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>氧化還原持續轉移電子</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>氫氣(鎂較活潑)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>金,活性小較穩定</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>判斷</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>用活性解釋為何用碳而非金還原鐵礦？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>犧牲陽極防船體生鏽</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>活性極小不易氧化</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>活性大者置換溶液中活性小者</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>碳便宜且活性足以還原鐵</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>用活性順序判斷金與鐵誰較穩定？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>金,活性小較穩定</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>犧牲陽極防船體生鏽</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>氧化還原持續轉移電子</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>元素態(如金)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>活性</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>海邊鐵構造裝鋅塊的原理？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>元素態(如金)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>鋅活性大先氧化保護鐵</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>鋅活性&gt;鐵先氧化;錫活性&lt;鐵破損後鐵先鏽</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>金,活性小較穩定</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>犧牲陽極</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下2-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>順序</t>
+          <t>順序：每種金屬都有固定的活性大小，活性越大代表越容易發生化學反應</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>置換</t>
+          <t>置換：活性大的金屬會把溶液裡活性小的金屬離子的位置搶走，讓它變回金屬析出</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>穩定</t>
+          <t>穩定：金是活性非常小的金屬，很不容易和其他物質反應，所以能長久保持光澤</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：電池內部的化學反應會釋放能量，這些能量被轉換成我們可以使用的電能</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>犧牲</t>
+          <t>犧牲：在鐵的表面鍍上一層鋅，讓活性較大的鋅代替鐵先被氧化，藉此保護裡面的鐵</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>置換</t>
+          <t>置換：鐵的活性比銅大，會把硫酸銅溶液中的銅離子置換出來，變成銅附著在鐵上</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>穩定</t>
+          <t>穩定：金的活性非常小，很難和空氣中的氧或其他物質反應，所以顏色能一直保持不變</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>較活潑</t>
+          <t>較活潑：鎂在金屬活性順序表中排在鐵前面，代表鎂比鐵更容易發生化學反應</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>順序</t>
+          <t>順序：把各種金屬依照反應活潑程度由大到小排列出來的順序，稱為金屬活性順序</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>活潑</t>
+          <t>活潑：活性越大的金屬，越容易和其他物質發生反應，也越容易被氧化</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>鋅活性大</t>
+          <t>鋅活性大：鋅的活性比銅大，能把硫酸銅溶液中的銅離子取代出來，變成金屬銅附著在鋅片上</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>銅活性小</t>
+          <t>銅活性小：銅的活性比鋅小，沒有能力搶走鋅離子的位置，所以放進去不會發生反應</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>產電</t>
+          <t>產電：乾電池內部靠金屬和化學物質進行氧化還原反應，過程中釋放的電子形成電流</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>犧牲陽極</t>
+          <t>犧牲陽極：即使鍍層被刮破露出鐵，活性較大的鋅還是會搶先和氧氣反應，保護底下的鐵</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>極活潑</t>
+          <t>極活潑：鉀和鈉排在金屬活性順序表的最前面，代表它們是反應性非常強、極為活潑的金屬</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>置換</t>
+          <t>置換：鐵把溶液中的銅離子置換出來，銅附著在鐵釘表面，讓鐵釘看起來變成紅棕色</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>穩定</t>
+          <t>穩定：因為活性小的金屬不容易和其他物質反應，所以能以純金屬的形態單獨存在於自然界中</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>先氧化</t>
+          <t>先氧化：保護用的金屬活性一定要比被保護的金屬更大，才能搶先氧化，替它擋下腐蝕</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>置換</t>
+          <t>置換：鐵的活性比銅大，會把硫酸銅溶液中的銅離子置換出來，析出紅色的銅附著在鐵的表面，這是一種置換反應</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：乾電池內部利用金屬活性不同產生的化學反應，把儲存的化學能轉換成可以使用的電能</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>活性</t>
+          <t>活性：鋅比鐵活潑會搶先氧化保護鐵；但錫比鐵不活潑，鍍層一旦破損，反而是鐵先生鏽</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>機制：只要電池內部的氧化還原反應還在進行，電子就會持續從一極流向另一極，形成電流</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>規則：只要把三種金屬按活性大小排好，活性排在前面的金屬就能置換出活性排在後面的金屬離子</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>保護：鋅塊的活性比船體鋼鐵大，會優先和海水中的氧反應，代替船體被腐蝕，達到保護效果</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>穩定</t>
+          <t>穩定：金和銀的活性都非常小，幾乎不會和空氣中的氧或水氣反應，所以表面能一直維持光亮</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>反應</t>
+          <t>反應：活性較大的鎂會和鹽酸反應，把酸裡的氫離子變成氫氣冒出來，形成氣泡</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>判斷</t>
+          <t>判斷：只要金屬在活性順序表上排在氫的前面，它就能和酸反應並產生氫氣</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：碳的取得成本低，而且活性夠強，足以把鐵礦中的氧搶走還原出鐵，不需要用到昂貴的金</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>活性</t>
+          <t>活性：金在金屬活性順序中排在很後面，活性很小、非常不容易和其他物質反應，因此比鐵更穩定，這也是金不容易生鏽的原因</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>犧牲陽極</t>
+          <t>犧牲陽極：鋅的活性比鐵大，接上鋅塊後，鋅會優先被氧化腐蝕、犧牲自己，藉此保護活性較小的鐵構造不容易生鏽，這種方法稱為犧牲陽極保護法</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下2-3_三種難度測驗卷.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>不會</t>
+          <t>活性順序</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>電能</t>
+          <t>小的金屬</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>鉀/鈉</t>
+          <t>鐵</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -603,17 +603,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>小</t>
+          <t>活性大小</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>活性順序</t>
+          <t>表面析出銅</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>反應或氧化</t>
+          <t>鋅</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>活性順序</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>電能</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>置換出銅</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>銅</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>鐵</t>
+          <t>不會</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>小</t>
+          <t>活性順序</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>活性大小</t>
+          <t>鋅</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>小的金屬</t>
+          <t>活性順序</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>鉀/鈉</t>
+          <t>電能</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>活性大小</t>
+          <t>置換出銅</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>鋅</t>
+          <t>表面析出銅</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>表面析出銅</t>
+          <t>小的金屬</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>鉀/鈉</t>
+          <t>銅</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1044,17 +1044,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>大</t>
+          <t>電能</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>鉀/鈉</t>
+          <t>小</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>活性大小</t>
+          <t>小的金屬</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1244,17 +1244,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>活性大小</t>
+          <t>小的金屬</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>小</t>
+          <t>電能</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>鐵</t>
+          <t>大</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>電能</t>
+          <t>鐵</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>置換出銅</t>
+          <t>銅</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>活性大小</t>
+          <t>活性順序</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1364,12 +1364,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>電能</t>
+          <t>鋅</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>大</t>
+          <t>小的金屬</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
